--- a/LieMappBench/Attack-Library/attack_library.xlsx
+++ b/LieMappBench/Attack-Library/attack_library.xlsx
@@ -5,19 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0fb6dd92c3d3ce1e/1-대학원/1-과제/1-AI포렌식/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mindol\AI-Forensics\LieMapp\LieMappBench\Attack-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="264" documentId="11_DDB2146940E06A69FB958C249F9758F4547CFCCC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96F65EF2-4D1D-44EC-84A0-EB479C36F273}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4772F06E-1EDC-4647-9E07-A8CD97C5549E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-60" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI 포렌식" sheetId="1" r:id="rId1"/>
     <sheet name="권장저널&amp;학회의 사본" sheetId="3" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -1160,7 +1159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="210">
   <si>
     <t>논문 선정 방법</t>
   </si>
@@ -2091,6 +2090,30 @@
 DC1. python/sglang/srt/models/transformers.py:1463 (_encode_modality_items)
 DC2. python/sglang/srt/models/transformers.py:1488 (_encode_modality_items)
 DC3. python/sglang/srt/models/transformers.py:1488 (_encode_modality_items).</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>NeurIPS 2025</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attractive Metadata Attck: Inducing LLM Agents to Invoke Malicious Tools</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Excessive Agency</t>
+  </si>
+  <si>
+    <t>Unapproved High-Impact Actions</t>
+  </si>
+  <si>
+    <t>DC1: LLM Agent가 최종적으로 선택한 도구의 메타데이터를, 기록할 수 있는가?
+DC2: LLM Agent가 선택한 도구의 실제 호출 여부와, 호출 시 도구에 전달한 매개변수를 기록할 수 있는가?</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>AC1: LLM Agent가 도구의 이름과 설명을 읽고, 사용할 도구를 스스로 선택하는가? 아니면, 특정 프롬프트에 대해서는 사용할 도구가 정해져있는가?
+AC2: LLM Agent가 선택한 도구 호출 시, 추론 엔진이 해당 도구의 메타데이터의 보안성에 대해 검토하는가?</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -2469,7 +2492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2556,34 +2579,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2646,6 +2649,32 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2821,10 +2850,6 @@
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3050,277 +3075,293 @@
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="66" t="s">
         <v>193</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
     </row>
     <row r="3" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
     </row>
     <row r="4" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="49" t="s">
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="65" t="s">
         <v>189</v>
       </c>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="49"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
     </row>
     <row r="5" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="50" t="s">
+      <c r="D5" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="42" t="s">
         <v>173</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="G5" s="50" t="s">
+      <c r="G5" s="42" t="s">
         <v>191</v>
       </c>
-      <c r="H5" s="50" t="s">
+      <c r="H5" s="42" t="s">
         <v>190</v>
       </c>
-      <c r="I5" s="52" t="s">
+      <c r="I5" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="J5" s="52" t="s">
+      <c r="J5" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="K5" s="52" t="s">
+      <c r="K5" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="L5" s="52" t="s">
+      <c r="L5" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="M5" s="52" t="s">
+      <c r="M5" s="44" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="55" t="s">
+      <c r="B6" s="46"/>
+      <c r="C6" s="47" t="s">
         <v>165</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="59" t="s">
         <v>182</v>
       </c>
-      <c r="F6" s="67" t="s">
+      <c r="F6" s="59" t="s">
         <v>174</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="H6" s="69" t="s">
+      <c r="H6" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="J6" s="69" t="s">
+      <c r="J6" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="K6" s="69" t="s">
+      <c r="K6" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="L6" s="69" t="s">
+      <c r="L6" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="M6" s="69" t="s">
+      <c r="M6" s="61" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="67.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="50" t="s">
         <v>163</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="60" t="s">
+      <c r="B7" s="51"/>
+      <c r="C7" s="52" t="s">
         <v>167</v>
       </c>
-      <c r="D7" s="60" t="s">
+      <c r="D7" s="52" t="s">
         <v>166</v>
       </c>
-      <c r="E7" s="59" t="s">
+      <c r="E7" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="F7" s="59" t="s">
+      <c r="F7" s="51" t="s">
         <v>175</v>
       </c>
-      <c r="G7" s="68" t="s">
+      <c r="G7" s="60" t="s">
         <v>195</v>
       </c>
-      <c r="H7" s="70" t="s">
+      <c r="H7" s="62" t="s">
         <v>192</v>
       </c>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="69"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
     </row>
     <row r="8" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="61"/>
-      <c r="B8" s="62"/>
-      <c r="C8" s="63" t="s">
+      <c r="A8" s="53"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="55" t="s">
         <v>169</v>
       </c>
-      <c r="D8" s="63" t="s">
+      <c r="D8" s="55" t="s">
         <v>168</v>
       </c>
-      <c r="E8" s="62" t="s">
+      <c r="E8" s="54" t="s">
         <v>180</v>
       </c>
-      <c r="F8" s="62" t="s">
+      <c r="F8" s="54" t="s">
         <v>176</v>
       </c>
-      <c r="G8" s="69" t="s">
+      <c r="G8" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="H8" s="69" t="s">
+      <c r="H8" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="I8" s="69" t="s">
+      <c r="I8" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="J8" s="69" t="s">
+      <c r="J8" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="K8" s="69" t="s">
+      <c r="K8" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="L8" s="69" t="s">
+      <c r="L8" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="M8" s="69" t="s">
+      <c r="M8" s="61" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="45" x14ac:dyDescent="0.2">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="56" t="s">
         <v>163</v>
       </c>
-      <c r="B9" s="64"/>
-      <c r="C9" s="65" t="s">
+      <c r="B9" s="56"/>
+      <c r="C9" s="57" t="s">
         <v>171</v>
       </c>
-      <c r="D9" s="66" t="s">
+      <c r="D9" s="58" t="s">
         <v>170</v>
       </c>
-      <c r="E9" s="57" t="s">
+      <c r="E9" s="49" t="s">
         <v>181</v>
       </c>
-      <c r="F9" s="57" t="s">
+      <c r="F9" s="49" t="s">
         <v>178</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="G9" s="60" t="s">
         <v>196</v>
       </c>
-      <c r="H9" s="70" t="s">
+      <c r="H9" s="62" t="s">
         <v>192</v>
       </c>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="69"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="61"/>
     </row>
     <row r="10" spans="1:13" ht="128.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="64" t="s">
+      <c r="A10" s="56" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="64"/>
-      <c r="C10" s="65" t="s">
+      <c r="B10" s="56"/>
+      <c r="C10" s="57" t="s">
         <v>165</v>
       </c>
-      <c r="D10" s="66" t="s">
+      <c r="D10" s="58" t="s">
         <v>172</v>
       </c>
-      <c r="E10" s="57" t="s">
+      <c r="E10" s="49" t="s">
         <v>180</v>
       </c>
-      <c r="F10" s="57" t="s">
+      <c r="F10" s="49" t="s">
         <v>179</v>
       </c>
-      <c r="G10" s="68" t="s">
+      <c r="G10" s="60" t="s">
         <v>197</v>
       </c>
-      <c r="H10" s="68" t="s">
+      <c r="H10" s="60" t="s">
         <v>198</v>
       </c>
-      <c r="I10" s="68" t="s">
+      <c r="I10" s="60" t="s">
         <v>199</v>
       </c>
-      <c r="J10" s="68" t="s">
+      <c r="J10" s="60" t="s">
         <v>200</v>
       </c>
-      <c r="K10" s="68" t="s">
+      <c r="K10" s="60" t="s">
         <v>201</v>
       </c>
-      <c r="L10" s="68" t="s">
+      <c r="L10" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="M10" s="68" t="s">
+      <c r="M10" s="60" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="37"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
+    <row r="11" spans="1:13" ht="45" x14ac:dyDescent="0.2">
+      <c r="A11" s="56" t="s">
+        <v>163</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="D11" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" s="49" t="s">
+        <v>207</v>
+      </c>
+      <c r="G11" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="H11" s="64" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="12" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="37"/>
@@ -7180,27 +7221,27 @@
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
